--- a/data/comments/comments_relij_coded.xlsx
+++ b/data/comments/comments_relij_coded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joellattmann/Documents/GitHub/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6073E54A-76B4-8141-80D4-BF0A3745D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1E9E5-6F17-3543-BDB1-C60AA22FABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="880" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
+    <workbookView xWindow="980" yWindow="880" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -2397,8 +2397,24 @@
       <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="K7" s="8"/>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
       <c r="L7" t="s">
         <v>40</v>
       </c>
@@ -2422,8 +2438,24 @@
       <c r="E8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="K8" s="8"/>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
       <c r="L8" t="s">
         <v>43</v>
       </c>
@@ -2450,8 +2482,24 @@
       <c r="E9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="K9" s="8"/>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
       <c r="L9" t="s">
         <v>48</v>
       </c>
@@ -2475,8 +2523,24 @@
       <c r="E10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="K10" s="8"/>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>51</v>
       </c>
@@ -2503,8 +2567,24 @@
       <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="K11" s="8"/>
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
       <c r="L11" t="s">
         <v>54</v>
       </c>
@@ -2531,8 +2611,24 @@
       <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="K12" s="8"/>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
       <c r="L12" t="s">
         <v>58</v>
       </c>
@@ -2559,8 +2655,24 @@
       <c r="E13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="K13" s="8"/>
+      <c r="F13" s="7">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
       <c r="L13" t="s">
         <v>62</v>
       </c>
@@ -2584,8 +2696,24 @@
       <c r="E14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="K14" s="8"/>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
       <c r="L14" t="s">
         <v>65</v>
       </c>
@@ -2612,8 +2740,24 @@
       <c r="E15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="K15" s="8"/>
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
       <c r="L15" t="s">
         <v>69</v>
       </c>
@@ -2637,8 +2781,24 @@
       <c r="E16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="K16" s="8"/>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1</v>
+      </c>
       <c r="L16" t="s">
         <v>72</v>
       </c>
@@ -2662,8 +2822,24 @@
       <c r="E17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="K17" s="8"/>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
       <c r="L17" t="s">
         <v>76</v>
       </c>
@@ -2687,8 +2863,24 @@
       <c r="E18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="K18" s="8"/>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
       <c r="L18" t="s">
         <v>79</v>
       </c>
@@ -2715,8 +2907,24 @@
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="K19" s="8"/>
+      <c r="F19" s="7">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
       <c r="L19" t="s">
         <v>82</v>
       </c>
@@ -2743,8 +2951,24 @@
       <c r="E20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="K20" s="8"/>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
       <c r="L20" t="s">
         <v>86</v>
       </c>
@@ -2768,12 +2992,24 @@
       <c r="E21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="11"/>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10">
+        <v>3</v>
+      </c>
+      <c r="K21" s="11">
+        <v>0</v>
+      </c>
       <c r="L21" t="s">
         <v>89</v>
       </c>

--- a/data/comments/comments_relij_coded.xlsx
+++ b/data/comments/comments_relij_coded.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joellattmann/Documents/GitHub/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1E9E5-6F17-3543-BDB1-C60AA22FABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793C21FE-89DD-E043-A760-6E0995B75112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="880" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
+    <workbookView xWindow="900" yWindow="1080" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="comments_relij_coded" localSheetId="0">Tabelle1!$A$1:$T$151</definedName>
+    <definedName name="comments_relij_coded" localSheetId="0">Tabelle1!$A$1:$U$151</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="514">
   <si>
     <t>coder</t>
   </si>
@@ -1612,6 +1612,9 @@
   </si>
   <si>
     <t>Joël</t>
+  </si>
+  <si>
+    <t>unique_id</t>
   </si>
 </sst>
 </file>
@@ -1642,72 +1645,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1719,22 +1662,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1744,13 +1676,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2089,153 +2014,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E16AA77-9110-E641-A1FB-6E892B02F2D1}">
-  <dimension ref="A1:T151"/>
+  <dimension ref="A1:U151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="37" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" customWidth="1"/>
-    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="2" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>513</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>512</v>
       </c>
       <c r="B2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>6</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2">
         <v>3</v>
       </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>512</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B66" si="0">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>132</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -2246,37 +2180,41 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>512</v>
       </c>
       <c r="B4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>102</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="7">
-        <v>0</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -2287,37 +2225,41 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
         <v>30</v>
       </c>
-      <c r="M4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>512</v>
       </c>
       <c r="B5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -2325,207 +2267,227 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>512</v>
       </c>
       <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C6">
         <v>129</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>4</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
         <v>37</v>
       </c>
-      <c r="M6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>512</v>
       </c>
       <c r="B7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C7">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
         <v>40</v>
       </c>
-      <c r="M7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>512</v>
       </c>
       <c r="B8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>148</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="7">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <v>3</v>
       </c>
-      <c r="K8" s="8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
         <v>43</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>147</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>512</v>
       </c>
       <c r="B9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C9">
         <v>76</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="7">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>4</v>
       </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
         <v>48</v>
       </c>
-      <c r="M9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>512</v>
       </c>
       <c r="B10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C10">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -2536,40 +2498,44 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
         <v>51</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>44</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>512</v>
       </c>
       <c r="B11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C11">
         <v>146</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
       <c r="G11">
         <v>1</v>
       </c>
@@ -2580,42 +2546,46 @@
         <v>1</v>
       </c>
       <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
         <v>3</v>
       </c>
-      <c r="K11" s="8">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
         <v>54</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>32</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>512</v>
       </c>
       <c r="B12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C12">
         <v>167</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="7">
-        <v>0</v>
-      </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2624,207 +2594,227 @@
         <v>1</v>
       </c>
       <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
         <v>3</v>
       </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
         <v>58</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>156</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>512</v>
       </c>
       <c r="B13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C13">
         <v>56</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="7">
-        <v>0</v>
-      </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
-      <c r="K13" s="8">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
         <v>62</v>
       </c>
-      <c r="M13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>512</v>
       </c>
       <c r="B14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C14">
         <v>137</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
         <v>3</v>
       </c>
-      <c r="K14" s="8">
-        <v>1</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
         <v>65</v>
       </c>
-      <c r="M14">
-        <v>2</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>512</v>
       </c>
       <c r="B15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C15">
         <v>107</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>67</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="7">
-        <v>0</v>
-      </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>3</v>
       </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
         <v>69</v>
       </c>
-      <c r="M15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>512</v>
       </c>
       <c r="B16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C16">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>70</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <v>3</v>
       </c>
-      <c r="K16" s="8">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
         <v>72</v>
       </c>
-      <c r="M16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>512</v>
       </c>
       <c r="B17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C17">
         <v>9</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>73</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -2832,40 +2822,44 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
         <v>3</v>
       </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
         <v>76</v>
       </c>
-      <c r="M17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>512</v>
       </c>
       <c r="B18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C18">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>77</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2873,87 +2867,95 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
         <v>79</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>34</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>512</v>
       </c>
       <c r="B19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C19">
         <v>73</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>56</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="7">
-        <v>0</v>
-      </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
         <v>3</v>
       </c>
-      <c r="K19" s="8">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
         <v>82</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>69</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>512</v>
       </c>
       <c r="B20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C20">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="7">
-        <v>0</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2961,2279 +2963,4065 @@
         <v>0</v>
       </c>
       <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <v>4</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>3</v>
       </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
         <v>86</v>
       </c>
-      <c r="M20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>512</v>
       </c>
       <c r="B21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C21">
         <v>63</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>87</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="9">
-        <v>0</v>
-      </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
-      <c r="H21" s="10">
-        <v>0</v>
-      </c>
-      <c r="I21" s="10">
-        <v>0</v>
-      </c>
-      <c r="J21" s="10">
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
         <v>3</v>
       </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="L21" s="4">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
         <v>89</v>
       </c>
-      <c r="M21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>512</v>
       </c>
       <c r="B22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C22">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>90</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L22" t="s">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
         <v>92</v>
       </c>
-      <c r="M22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>512</v>
       </c>
       <c r="B23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C23">
         <v>118</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L23" t="s">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
         <v>94</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>116</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>512</v>
       </c>
       <c r="B24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C24">
         <v>76</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L24" t="s">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
         <v>98</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>74</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>512</v>
       </c>
       <c r="B25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C25">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>100</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L25" t="s">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
         <v>103</v>
       </c>
-      <c r="M25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>512</v>
       </c>
       <c r="B26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C26">
         <v>190</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>60</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L26" t="s">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
         <v>105</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>187</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>512</v>
       </c>
       <c r="B27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C27">
         <v>3</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>107</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L27" t="s">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
         <v>109</v>
       </c>
-      <c r="M27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>512</v>
       </c>
       <c r="B28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C28">
         <v>134</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>110</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L28" t="s">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
         <v>112</v>
       </c>
-      <c r="M28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>512</v>
       </c>
       <c r="B29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C29">
         <v>74</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>56</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L29" t="s">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
         <v>114</v>
       </c>
-      <c r="M29">
-        <v>2</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>512</v>
       </c>
       <c r="B30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C30">
         <v>78</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="L30" t="s">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
         <v>116</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>73</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>512</v>
       </c>
       <c r="B31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C31">
         <v>144</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>118</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L31" t="s">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
         <v>120</v>
       </c>
-      <c r="M31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>512</v>
       </c>
       <c r="B32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C32">
         <v>142</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>121</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L32" t="s">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
         <v>123</v>
       </c>
-      <c r="M32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>512</v>
       </c>
       <c r="B33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C33">
         <v>17</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>124</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L33" t="s">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
         <v>126</v>
       </c>
-      <c r="M33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>512</v>
       </c>
       <c r="B34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C34">
         <v>168</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>96</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L34" t="s">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
         <v>128</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>167</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>512</v>
       </c>
       <c r="B35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C35">
         <v>11</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>130</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="L35" t="s">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
         <v>132</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>10</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>512</v>
       </c>
       <c r="B36">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s">
         <v>134</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L36" t="s">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
         <v>137</v>
       </c>
-      <c r="M36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>512</v>
       </c>
       <c r="B37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C37">
         <v>154</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>87</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L37" t="s">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="s">
         <v>139</v>
       </c>
-      <c r="M37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>512</v>
       </c>
       <c r="B38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C38">
         <v>86</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>121</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="L38" t="s">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
         <v>141</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>77</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>512</v>
       </c>
       <c r="B39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C39">
         <v>28</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>143</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>135</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L39" t="s">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
         <v>145</v>
       </c>
-      <c r="M39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>512</v>
       </c>
       <c r="B40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C40">
         <v>158</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>96</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="L40" t="s">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
         <v>147</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>155</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>512</v>
       </c>
       <c r="B41">
-        <v>2</v>
-      </c>
-      <c r="C41" t="s">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
         <v>110</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>149</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L41" t="s">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
         <v>151</v>
       </c>
-      <c r="M41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>512</v>
       </c>
       <c r="B42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C42">
         <v>40</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>152</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L42" t="s">
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
         <v>154</v>
       </c>
-      <c r="M42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>512</v>
       </c>
       <c r="B43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C43">
         <v>7</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>155</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L43" t="s">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="s">
         <v>157</v>
       </c>
-      <c r="M43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>512</v>
       </c>
       <c r="B44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C44">
         <v>13</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>158</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L44" t="s">
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>3</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
         <v>160</v>
       </c>
-      <c r="M44" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>512</v>
       </c>
       <c r="B45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C45">
         <v>4</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>161</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L45" t="s">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>3</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
         <v>163</v>
       </c>
-      <c r="M45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>512</v>
       </c>
       <c r="B46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C46">
         <v>12</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>70</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>46</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L46" t="s">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>4</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
         <v>165</v>
       </c>
-      <c r="M46" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>512</v>
       </c>
       <c r="B47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C47">
         <v>11</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>166</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L47" t="s">
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>3</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
         <v>168</v>
       </c>
-      <c r="M47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>512</v>
       </c>
       <c r="B48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C48">
         <v>77</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>169</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>46</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L48" t="s">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
         <v>171</v>
       </c>
-      <c r="M48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>512</v>
       </c>
       <c r="B49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C49">
         <v>43</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>172</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L49" t="s">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
+        <v>3</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
         <v>174</v>
       </c>
-      <c r="M49" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>512</v>
       </c>
       <c r="B50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C50">
         <v>36</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>96</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L50" t="s">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
         <v>176</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>4</v>
       </c>
-      <c r="N50" s="1" t="s">
+      <c r="O50" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>512</v>
       </c>
       <c r="B51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C51">
         <v>66</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>118</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L51" t="s">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51">
+        <v>2</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
         <v>179</v>
       </c>
-      <c r="M51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>512</v>
       </c>
       <c r="B52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C52">
         <v>101</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>180</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>181</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L52" t="s">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
         <v>183</v>
       </c>
-      <c r="M52" t="s">
-        <v>24</v>
-      </c>
-      <c r="O52" t="s">
+      <c r="N52" t="s">
         <v>24</v>
       </c>
       <c r="P52" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>512</v>
       </c>
       <c r="B53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C53">
         <v>30</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>184</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>185</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="L53" t="s">
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
         <v>187</v>
       </c>
-      <c r="M53" t="s">
-        <v>24</v>
-      </c>
-      <c r="O53" t="s">
+      <c r="N53" t="s">
         <v>24</v>
       </c>
       <c r="P53" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>512</v>
       </c>
       <c r="B54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C54">
         <v>10</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>189</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="L54" t="s">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>3</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
         <v>191</v>
       </c>
-      <c r="M54" t="s">
-        <v>24</v>
-      </c>
-      <c r="O54" t="s">
+      <c r="N54" t="s">
         <v>24</v>
       </c>
       <c r="P54" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>512</v>
       </c>
       <c r="B55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C55">
         <v>37</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>192</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>193</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="L55" t="s">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>2</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
         <v>195</v>
       </c>
-      <c r="M55" t="s">
-        <v>24</v>
-      </c>
-      <c r="O55" t="s">
+      <c r="N55" t="s">
+        <v>24</v>
+      </c>
+      <c r="P55" t="s">
         <v>196</v>
       </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>512</v>
       </c>
       <c r="B56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C56">
         <v>38</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>198</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>181</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L56" t="s">
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>4</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
         <v>200</v>
       </c>
-      <c r="M56" t="s">
-        <v>24</v>
-      </c>
-      <c r="O56" t="s">
+      <c r="N56" t="s">
+        <v>24</v>
+      </c>
+      <c r="P56" t="s">
         <v>196</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>512</v>
       </c>
       <c r="B57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C57">
         <v>40</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>202</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>181</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L57" t="s">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
         <v>204</v>
       </c>
-      <c r="M57" t="s">
-        <v>24</v>
-      </c>
-      <c r="O57" t="s">
+      <c r="N57" t="s">
+        <v>24</v>
+      </c>
+      <c r="P57" t="s">
         <v>196</v>
       </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>512</v>
       </c>
       <c r="B58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C58">
         <v>36</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>205</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>206</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L58" t="s">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58">
+        <v>4</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
         <v>208</v>
       </c>
-      <c r="M58" t="s">
-        <v>24</v>
-      </c>
-      <c r="O58" t="s">
+      <c r="N58" t="s">
         <v>24</v>
       </c>
       <c r="P58" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>512</v>
       </c>
       <c r="B59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C59">
         <v>34</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>209</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="L59" t="s">
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>4</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="s">
         <v>211</v>
       </c>
-      <c r="M59" t="s">
-        <v>24</v>
-      </c>
-      <c r="O59" t="s">
+      <c r="N59" t="s">
         <v>24</v>
       </c>
       <c r="P59" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>512</v>
       </c>
       <c r="B60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C60">
         <v>18</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>212</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>213</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="L60" t="s">
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>2</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
         <v>215</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>4</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="O60" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="O60" t="s">
-        <v>24</v>
-      </c>
       <c r="P60" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>512</v>
       </c>
       <c r="B61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C61">
         <v>57</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>217</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>193</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L61" t="s">
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
         <v>219</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>36</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="O61" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="O61" t="s">
-        <v>24</v>
-      </c>
       <c r="P61" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>512</v>
       </c>
       <c r="B62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C62">
         <v>16</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>221</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>181</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="L62" t="s">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62">
+        <v>3</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
         <v>223</v>
       </c>
-      <c r="M62" t="s">
-        <v>24</v>
-      </c>
-      <c r="O62" t="s">
+      <c r="N62" t="s">
         <v>24</v>
       </c>
       <c r="P62" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>512</v>
       </c>
       <c r="B63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C63">
         <v>45</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>224</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>193</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L63" t="s">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
         <v>226</v>
       </c>
-      <c r="M63" t="s">
-        <v>24</v>
-      </c>
-      <c r="O63" t="s">
+      <c r="N63" t="s">
+        <v>24</v>
+      </c>
+      <c r="P63" t="s">
         <v>196</v>
       </c>
-      <c r="P63" t="s">
+      <c r="Q63" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>512</v>
       </c>
       <c r="B64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C64">
         <v>19</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>227</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>206</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="L64" t="s">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>4</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="s">
         <v>229</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>18</v>
       </c>
-      <c r="N64" s="1" t="s">
+      <c r="O64" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="O64" t="s">
-        <v>24</v>
-      </c>
       <c r="P64" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>512</v>
       </c>
       <c r="B65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C65">
         <v>80</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>224</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>181</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="L65" t="s">
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65">
+        <v>3</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
         <v>232</v>
       </c>
-      <c r="M65" t="s">
-        <v>24</v>
-      </c>
-      <c r="O65" t="s">
+      <c r="N65" t="s">
+        <v>24</v>
+      </c>
+      <c r="P65" t="s">
         <v>196</v>
       </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>512</v>
       </c>
       <c r="B66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C66">
         <v>46</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>234</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>193</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L66" t="s">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>2</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="s">
         <v>236</v>
       </c>
-      <c r="M66" t="s">
-        <v>24</v>
-      </c>
-      <c r="O66" t="s">
+      <c r="N66" t="s">
         <v>24</v>
       </c>
       <c r="P66" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>512</v>
       </c>
       <c r="B67">
+        <f t="shared" ref="B67:B130" si="1">ROW()-1</f>
+        <v>66</v>
+      </c>
+      <c r="C67">
         <v>52</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>237</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>189</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="L67" t="s">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
         <v>239</v>
       </c>
-      <c r="M67" t="s">
-        <v>24</v>
-      </c>
-      <c r="O67" t="s">
+      <c r="N67" t="s">
         <v>24</v>
       </c>
       <c r="P67" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>512</v>
       </c>
       <c r="B68">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="C68">
         <v>6</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>240</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>241</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="L68" t="s">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
         <v>243</v>
       </c>
-      <c r="M68" t="s">
-        <v>24</v>
-      </c>
-      <c r="O68" t="s">
+      <c r="N68" t="s">
+        <v>24</v>
+      </c>
+      <c r="P68" t="s">
         <v>196</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>512</v>
       </c>
       <c r="B69">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="C69">
         <v>28</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>245</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>181</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="L69" t="s">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="s">
         <v>247</v>
       </c>
-      <c r="M69" t="s">
-        <v>24</v>
-      </c>
-      <c r="O69" t="s">
+      <c r="N69" t="s">
         <v>24</v>
       </c>
       <c r="P69" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>512</v>
       </c>
       <c r="B70">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="C70">
         <v>68</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>248</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>193</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="L70" t="s">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>2</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
         <v>250</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>65</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="O70" t="s">
-        <v>24</v>
-      </c>
       <c r="P70" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>512</v>
       </c>
       <c r="B71">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="C71">
         <v>7</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>252</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="L71" t="s">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
         <v>254</v>
       </c>
-      <c r="M71" t="s">
-        <v>24</v>
-      </c>
-      <c r="O71" t="s">
+      <c r="N71" t="s">
+        <v>24</v>
+      </c>
+      <c r="P71" t="s">
         <v>196</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>512</v>
       </c>
       <c r="B72">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="C72">
         <v>19</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>255</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>193</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L72" t="s">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <v>2</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
         <v>257</v>
       </c>
-      <c r="M72" t="s">
-        <v>24</v>
-      </c>
-      <c r="O72" t="s">
+      <c r="N72" t="s">
         <v>24</v>
       </c>
       <c r="P72" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>512</v>
       </c>
       <c r="B73">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="C73">
         <v>13</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>258</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>193</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="L73" t="s">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
         <v>260</v>
       </c>
-      <c r="M73" t="s">
-        <v>24</v>
-      </c>
-      <c r="O73" t="s">
+      <c r="N73" t="s">
         <v>24</v>
       </c>
       <c r="P73" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>512</v>
       </c>
       <c r="B74">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="C74">
         <v>32</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>261</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>181</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="L74" t="s">
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="s">
         <v>263</v>
       </c>
-      <c r="M74" t="s">
-        <v>24</v>
-      </c>
-      <c r="O74" t="s">
+      <c r="N74" t="s">
         <v>24</v>
       </c>
       <c r="P74" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>512</v>
       </c>
       <c r="B75">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="C75">
         <v>15</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>202</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>189</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="F75" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="L75" t="s">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>4</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="s">
         <v>265</v>
       </c>
-      <c r="M75" t="s">
-        <v>24</v>
-      </c>
-      <c r="O75" t="s">
+      <c r="N75" t="s">
         <v>24</v>
       </c>
       <c r="P75" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>512</v>
       </c>
       <c r="B76">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="C76">
         <v>9</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>266</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>193</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="L76" t="s">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76">
+        <v>4</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
         <v>268</v>
       </c>
-      <c r="M76" t="s">
-        <v>24</v>
-      </c>
-      <c r="O76" t="s">
+      <c r="N76" t="s">
         <v>24</v>
       </c>
       <c r="P76" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>512</v>
       </c>
       <c r="B77">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="C77">
         <v>17</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>221</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>181</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="L77" t="s">
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
         <v>270</v>
       </c>
-      <c r="M77">
-        <v>2</v>
-      </c>
-      <c r="N77" s="1" t="s">
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O77" t="s">
-        <v>24</v>
-      </c>
       <c r="P77" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>512</v>
       </c>
       <c r="B78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="C78">
         <v>56</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>271</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>193</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="L78" t="s">
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="s">
         <v>273</v>
       </c>
-      <c r="M78" t="s">
-        <v>24</v>
-      </c>
-      <c r="O78" t="s">
+      <c r="N78" t="s">
         <v>24</v>
       </c>
       <c r="P78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>512</v>
       </c>
       <c r="B79">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="C79">
         <v>32</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>274</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>193</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="L79" t="s">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79" t="s">
         <v>276</v>
       </c>
-      <c r="M79">
-        <v>2</v>
-      </c>
-      <c r="N79" s="1" t="s">
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="O79" t="s">
-        <v>24</v>
-      </c>
       <c r="P79" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>512</v>
       </c>
       <c r="B80">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="C80">
         <v>21</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>227</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>193</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="L80" t="s">
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>4</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
         <v>279</v>
       </c>
-      <c r="M80" t="s">
-        <v>24</v>
-      </c>
-      <c r="O80" t="s">
+      <c r="N80" t="s">
+        <v>24</v>
+      </c>
+      <c r="P80" t="s">
         <v>196</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>512</v>
       </c>
       <c r="B81">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="C81">
         <v>28</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>248</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>185</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L81" t="s">
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>3</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="s">
         <v>281</v>
       </c>
-      <c r="M81" t="s">
-        <v>24</v>
-      </c>
-      <c r="O81" t="s">
+      <c r="N81" t="s">
         <v>24</v>
       </c>
       <c r="P81" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>512</v>
       </c>
       <c r="B82">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="C82">
         <v>34</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>282</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>181</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="L82" t="s">
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>4</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" t="s">
         <v>284</v>
       </c>
-      <c r="M82" t="s">
-        <v>24</v>
-      </c>
-      <c r="O82" t="s">
+      <c r="N82" t="s">
         <v>24</v>
       </c>
       <c r="P82" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>512</v>
       </c>
       <c r="B83">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="C83">
         <v>41</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>285</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>193</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="L83" t="s">
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83">
+        <v>2</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" t="s">
         <v>287</v>
       </c>
-      <c r="M83" t="s">
-        <v>24</v>
-      </c>
-      <c r="O83" t="s">
+      <c r="N83" t="s">
         <v>24</v>
       </c>
       <c r="P83" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>512</v>
       </c>
       <c r="B84">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="C84">
         <v>89</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>288</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>181</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="L84" t="s">
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84" t="s">
         <v>290</v>
       </c>
-      <c r="M84" t="s">
-        <v>24</v>
-      </c>
-      <c r="O84" t="s">
+      <c r="N84" t="s">
         <v>24</v>
       </c>
       <c r="P84" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>512</v>
       </c>
       <c r="B85">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="C85">
         <v>90</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>291</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>181</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L85" t="s">
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>3</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
         <v>293</v>
       </c>
-      <c r="M85" t="s">
-        <v>24</v>
-      </c>
-      <c r="O85" t="s">
+      <c r="N85" t="s">
         <v>24</v>
       </c>
       <c r="P85" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>512</v>
       </c>
       <c r="B86">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="C86">
         <v>42</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>294</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>189</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L86" t="s">
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>3</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
         <v>296</v>
       </c>
-      <c r="M86">
+      <c r="N86">
         <v>4</v>
       </c>
-      <c r="N86" s="1" t="s">
+      <c r="O86" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="O86" t="s">
-        <v>24</v>
-      </c>
       <c r="P86" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>512</v>
       </c>
       <c r="B87">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="C87">
         <v>9</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>298</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>213</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="L87" t="s">
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>3</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" t="s">
         <v>300</v>
       </c>
-      <c r="M87" t="s">
-        <v>24</v>
-      </c>
-      <c r="O87" t="s">
+      <c r="N87" t="s">
         <v>24</v>
       </c>
       <c r="P87" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>512</v>
       </c>
       <c r="B88">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="C88">
         <v>3</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>301</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>206</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L88" t="s">
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>4</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88" t="s">
         <v>303</v>
       </c>
-      <c r="M88" t="s">
-        <v>24</v>
-      </c>
-      <c r="O88" t="s">
+      <c r="N88" t="s">
+        <v>24</v>
+      </c>
+      <c r="P88" t="s">
         <v>196</v>
       </c>
-      <c r="P88" t="s">
+      <c r="Q88" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>512</v>
       </c>
       <c r="B89">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="C89">
         <v>47</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>305</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>206</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="L89" t="s">
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3</v>
+      </c>
+      <c r="K89">
+        <v>4</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
         <v>307</v>
       </c>
-      <c r="M89" t="s">
-        <v>24</v>
-      </c>
-      <c r="O89" t="s">
+      <c r="N89" t="s">
         <v>24</v>
       </c>
       <c r="P89" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>512</v>
       </c>
       <c r="B90">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="C90">
         <v>50</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>308</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>181</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="F90" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="L90" t="s">
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>7</v>
+      </c>
+      <c r="K90">
+        <v>2</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
         <v>310</v>
       </c>
-      <c r="M90" t="s">
-        <v>24</v>
-      </c>
-      <c r="O90" t="s">
+      <c r="N90" t="s">
         <v>24</v>
       </c>
       <c r="P90" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>512</v>
       </c>
       <c r="B91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="C91">
         <v>8</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>311</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>193</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L91" t="s">
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>5</v>
+      </c>
+      <c r="K91">
+        <v>2</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91" t="s">
         <v>313</v>
       </c>
-      <c r="M91" t="s">
-        <v>24</v>
-      </c>
-      <c r="O91" t="s">
+      <c r="N91" t="s">
         <v>24</v>
       </c>
       <c r="P91" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>512</v>
       </c>
       <c r="B92">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="C92">
         <v>81</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>314</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>181</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="L92" t="s">
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>7</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92" t="s">
         <v>316</v>
       </c>
-      <c r="M92" t="s">
-        <v>24</v>
-      </c>
-      <c r="O92" t="s">
+      <c r="N92" t="s">
+        <v>24</v>
+      </c>
+      <c r="P92" t="s">
         <v>196</v>
       </c>
-      <c r="P92" t="s">
+      <c r="Q92" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>512</v>
       </c>
       <c r="B93">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="C93">
         <v>65</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>318</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>193</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="L93" t="s">
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
         <v>319</v>
       </c>
-      <c r="M93" t="s">
-        <v>24</v>
-      </c>
-      <c r="O93" t="s">
+      <c r="N93" t="s">
         <v>24</v>
       </c>
       <c r="P93" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>512</v>
       </c>
       <c r="B94">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="C94">
         <v>19</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>217</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>189</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="F94" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="L94" t="s">
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94" t="s">
         <v>321</v>
       </c>
-      <c r="M94">
-        <v>2</v>
-      </c>
-      <c r="N94" s="1" t="s">
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="O94" t="s">
-        <v>24</v>
-      </c>
       <c r="P94" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>512</v>
       </c>
       <c r="B95">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="C95">
         <v>35</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>248</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>206</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L95" t="s">
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>3</v>
+      </c>
+      <c r="K95">
+        <v>2</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" t="s">
         <v>324</v>
       </c>
-      <c r="M95" t="s">
-        <v>24</v>
-      </c>
-      <c r="O95" t="s">
+      <c r="N95" t="s">
         <v>24</v>
       </c>
       <c r="P95" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>512</v>
       </c>
       <c r="B96">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="C96">
         <v>32</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>325</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>206</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="L96" t="s">
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>8</v>
+      </c>
+      <c r="K96">
+        <v>2</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96" t="s">
         <v>327</v>
       </c>
-      <c r="M96" t="s">
-        <v>24</v>
-      </c>
-      <c r="O96" t="s">
+      <c r="N96" t="s">
         <v>24</v>
       </c>
       <c r="P96" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>512</v>
       </c>
       <c r="B97">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="C97">
         <v>61</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>248</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>181</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="L97" t="s">
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" t="s">
         <v>329</v>
       </c>
-      <c r="M97" t="s">
-        <v>24</v>
-      </c>
-      <c r="O97" t="s">
+      <c r="N97" t="s">
         <v>24</v>
       </c>
       <c r="P97" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>512</v>
       </c>
       <c r="B98">
-        <v>24</v>
-      </c>
-      <c r="C98" t="s">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="C98">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
         <v>330</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>206</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L98" t="s">
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3</v>
+      </c>
+      <c r="K98">
+        <v>4</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
         <v>332</v>
       </c>
-      <c r="M98" t="s">
-        <v>24</v>
-      </c>
-      <c r="O98" t="s">
+      <c r="N98" t="s">
+        <v>24</v>
+      </c>
+      <c r="P98" t="s">
         <v>196</v>
       </c>
-      <c r="P98" t="s">
+      <c r="Q98" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>512</v>
       </c>
       <c r="B99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="C99">
         <v>62</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>334</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>181</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="L99" t="s">
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>4</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" t="s">
         <v>336</v>
       </c>
-      <c r="M99" t="s">
-        <v>24</v>
-      </c>
-      <c r="O99" t="s">
+      <c r="N99" t="s">
         <v>24</v>
       </c>
       <c r="P99" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>512</v>
       </c>
       <c r="B100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="C100">
         <v>39</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>337</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>193</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="L100" t="s">
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>4</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
         <v>339</v>
       </c>
-      <c r="M100" t="s">
-        <v>24</v>
-      </c>
-      <c r="O100" t="s">
+      <c r="N100" t="s">
         <v>24</v>
       </c>
       <c r="P100" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>512</v>
       </c>
       <c r="B101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="C101">
         <v>95</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>340</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>181</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="F101" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L101" t="s">
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>4</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101" t="s">
         <v>342</v>
       </c>
-      <c r="M101" t="s">
-        <v>24</v>
-      </c>
-      <c r="O101" t="s">
+      <c r="N101" t="s">
         <v>24</v>
       </c>
       <c r="P101" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>512</v>
       </c>
       <c r="B102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="C102">
         <v>6</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>343</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>344</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="F102" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="L102" t="s">
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102" t="s">
         <v>346</v>
       </c>
-      <c r="M102" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q102" t="s">
+      <c r="N102" t="s">
         <v>24</v>
       </c>
       <c r="R102" t="s">
@@ -5245,30 +7033,52 @@
       <c r="T102" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>512</v>
       </c>
       <c r="B103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="C103">
         <v>4</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>347</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>348</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="F103" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="L103" t="s">
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" t="s">
         <v>350</v>
       </c>
-      <c r="M103" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q103" t="s">
+      <c r="N103" t="s">
         <v>24</v>
       </c>
       <c r="R103" t="s">
@@ -5280,100 +7090,166 @@
       <c r="T103" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>512</v>
       </c>
       <c r="B104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="C104">
         <v>31</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>351</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>352</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="F104" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="L104" t="s">
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104">
+        <v>4</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104" t="s">
         <v>354</v>
       </c>
-      <c r="M104" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q104" t="s">
+      <c r="N104" t="s">
+        <v>24</v>
+      </c>
+      <c r="R104" t="s">
         <v>196</v>
       </c>
-      <c r="R104" t="s">
+      <c r="S104" t="s">
         <v>355</v>
       </c>
-      <c r="S104" t="s">
-        <v>24</v>
-      </c>
       <c r="T104" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>512</v>
       </c>
       <c r="B105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="C105">
         <v>33</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>356</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>357</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L105" t="s">
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>4</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105" t="s">
         <v>359</v>
       </c>
-      <c r="M105" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q105" t="s">
+      <c r="N105" t="s">
+        <v>24</v>
+      </c>
+      <c r="R105" t="s">
         <v>196</v>
       </c>
-      <c r="R105" t="s">
+      <c r="S105" t="s">
         <v>360</v>
       </c>
-      <c r="S105" t="s">
-        <v>24</v>
-      </c>
       <c r="T105" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>512</v>
       </c>
       <c r="B106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="C106">
         <v>22</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>361</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>362</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="L106" t="s">
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106" t="s">
         <v>364</v>
       </c>
-      <c r="M106" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q106" t="s">
+      <c r="N106" t="s">
         <v>24</v>
       </c>
       <c r="R106" t="s">
@@ -5385,65 +7261,109 @@
       <c r="T106" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>512</v>
       </c>
       <c r="B107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="C107">
         <v>14</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>365</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>362</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="F107" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="L107" t="s">
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>4</v>
+      </c>
+      <c r="K107">
+        <v>4</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107" t="s">
         <v>367</v>
       </c>
-      <c r="M107" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q107" t="s">
+      <c r="N107" t="s">
+        <v>24</v>
+      </c>
+      <c r="R107" t="s">
         <v>196</v>
       </c>
-      <c r="R107" t="s">
+      <c r="S107" t="s">
         <v>368</v>
       </c>
-      <c r="S107" t="s">
-        <v>24</v>
-      </c>
       <c r="T107" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>512</v>
       </c>
       <c r="B108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="C108">
         <v>26</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>369</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>362</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="F108" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="L108" t="s">
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>4</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108" t="s">
         <v>371</v>
       </c>
-      <c r="M108" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q108" t="s">
+      <c r="N108" t="s">
         <v>24</v>
       </c>
       <c r="R108" t="s">
@@ -5455,30 +7375,52 @@
       <c r="T108" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U108" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>512</v>
       </c>
       <c r="B109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="C109">
         <v>14</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>372</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>357</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="L109" t="s">
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109" t="s">
         <v>374</v>
       </c>
-      <c r="M109" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q109" t="s">
+      <c r="N109" t="s">
         <v>24</v>
       </c>
       <c r="R109" t="s">
@@ -5490,30 +7432,52 @@
       <c r="T109" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U109" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>512</v>
       </c>
       <c r="B110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="C110">
         <v>113</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>375</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>352</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="F110" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="L110" t="s">
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>2</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" t="s">
         <v>377</v>
       </c>
-      <c r="M110" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q110" t="s">
+      <c r="N110" t="s">
         <v>24</v>
       </c>
       <c r="R110" t="s">
@@ -5525,246 +7489,400 @@
       <c r="T110" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>512</v>
       </c>
       <c r="B111">
-        <v>2</v>
-      </c>
-      <c r="C111" t="s">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
         <v>378</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>348</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="L111" t="s">
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>3</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" t="s">
         <v>380</v>
       </c>
-      <c r="M111" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q111" t="s">
+      <c r="N111" t="s">
+        <v>24</v>
+      </c>
+      <c r="R111" t="s">
         <v>196</v>
       </c>
-      <c r="R111" t="s">
+      <c r="S111" t="s">
         <v>381</v>
       </c>
-      <c r="S111" t="s">
-        <v>24</v>
-      </c>
       <c r="T111" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>512</v>
       </c>
       <c r="B112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="C112">
         <v>73</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>382</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>352</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="F112" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="L112" t="s">
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>4</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112" t="s">
         <v>384</v>
       </c>
-      <c r="M112">
+      <c r="N112">
         <v>50</v>
       </c>
-      <c r="N112" s="1" t="s">
+      <c r="O112" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="Q112" t="s">
-        <v>24</v>
-      </c>
       <c r="R112" t="s">
         <v>24</v>
       </c>
       <c r="S112" t="s">
+        <v>24</v>
+      </c>
+      <c r="T112" t="s">
         <v>386</v>
       </c>
-      <c r="T112" t="s">
+      <c r="U112" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>512</v>
       </c>
       <c r="B113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="C113">
         <v>6</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>387</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>362</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="F113" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="L113" t="s">
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113" t="s">
         <v>389</v>
       </c>
-      <c r="M113">
-        <v>2</v>
-      </c>
-      <c r="N113" s="1" t="s">
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="Q113" t="s">
+      <c r="R113" t="s">
         <v>196</v>
       </c>
-      <c r="R113" t="s">
+      <c r="S113" t="s">
         <v>391</v>
       </c>
-      <c r="S113" t="s">
-        <v>24</v>
-      </c>
       <c r="T113" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>512</v>
       </c>
       <c r="B114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="C114">
         <v>29</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>392</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>393</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="F114" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L114" t="s">
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114" t="s">
         <v>395</v>
       </c>
-      <c r="M114" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q114" t="s">
+      <c r="N114" t="s">
+        <v>24</v>
+      </c>
+      <c r="R114" t="s">
         <v>196</v>
       </c>
-      <c r="R114" t="s">
+      <c r="S114" t="s">
         <v>360</v>
       </c>
-      <c r="S114" t="s">
-        <v>24</v>
-      </c>
       <c r="T114" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>512</v>
       </c>
       <c r="B115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="C115">
         <v>50</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>396</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>352</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="F115" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="L115" t="s">
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>3</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115" t="s">
         <v>397</v>
       </c>
-      <c r="M115" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q115" t="s">
+      <c r="N115" t="s">
+        <v>24</v>
+      </c>
+      <c r="R115" t="s">
         <v>196</v>
       </c>
-      <c r="R115" t="s">
+      <c r="S115" t="s">
         <v>398</v>
       </c>
-      <c r="S115" t="s">
-        <v>24</v>
-      </c>
       <c r="T115" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="116" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>512</v>
       </c>
       <c r="B116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="C116">
         <v>15</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>399</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>352</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="L116" t="s">
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" t="s">
         <v>401</v>
       </c>
-      <c r="M116" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q116" t="s">
+      <c r="N116" t="s">
+        <v>24</v>
+      </c>
+      <c r="R116" t="s">
         <v>196</v>
       </c>
-      <c r="R116" t="s">
+      <c r="S116" t="s">
         <v>402</v>
       </c>
-      <c r="S116" t="s">
+      <c r="T116" t="s">
         <v>386</v>
       </c>
-      <c r="T116" t="s">
+      <c r="U116" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>512</v>
       </c>
       <c r="B117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="C117">
         <v>101</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>404</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>352</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="F117" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="L117" t="s">
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>5</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117" t="s">
         <v>406</v>
       </c>
-      <c r="M117" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q117" t="s">
+      <c r="N117" t="s">
         <v>24</v>
       </c>
       <c r="R117" t="s">
@@ -5776,30 +7894,52 @@
       <c r="T117" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U117" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>512</v>
       </c>
       <c r="B118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="C118">
         <v>26</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>407</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>408</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="F118" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="L118" t="s">
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118">
+        <v>2</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118" t="s">
         <v>410</v>
       </c>
-      <c r="M118" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q118" t="s">
+      <c r="N118" t="s">
         <v>24</v>
       </c>
       <c r="R118" t="s">
@@ -5811,65 +7951,109 @@
       <c r="T118" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>512</v>
       </c>
       <c r="B119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="C119">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>411</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>357</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="L119" t="s">
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119">
+        <v>3</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" t="s">
         <v>413</v>
       </c>
-      <c r="M119" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q119" t="s">
+      <c r="N119" t="s">
+        <v>24</v>
+      </c>
+      <c r="R119" t="s">
         <v>196</v>
       </c>
-      <c r="R119" t="s">
+      <c r="S119" t="s">
         <v>360</v>
       </c>
-      <c r="S119" t="s">
-        <v>24</v>
-      </c>
       <c r="T119" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="120" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>512</v>
       </c>
       <c r="B120">
-        <v>24</v>
-      </c>
-      <c r="C120" t="s">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="C120">
+        <v>24</v>
+      </c>
+      <c r="D120" t="s">
         <v>411</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>393</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="F120" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="L120" t="s">
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" t="s">
         <v>415</v>
       </c>
-      <c r="M120" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q120" t="s">
+      <c r="N120" t="s">
         <v>24</v>
       </c>
       <c r="R120" t="s">
@@ -5881,135 +8065,223 @@
       <c r="T120" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>512</v>
       </c>
       <c r="B121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="C121">
         <v>26</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>416</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>357</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="L121" t="s">
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121">
+        <v>2</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" t="s">
         <v>418</v>
       </c>
-      <c r="M121" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q121" t="s">
+      <c r="N121" t="s">
+        <v>24</v>
+      </c>
+      <c r="R121" t="s">
         <v>196</v>
       </c>
-      <c r="R121" t="s">
+      <c r="S121" t="s">
         <v>419</v>
       </c>
-      <c r="S121" t="s">
-        <v>24</v>
-      </c>
       <c r="T121" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="122" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>512</v>
       </c>
       <c r="B122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="C122">
         <v>27</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>420</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>352</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="F122" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="L122" t="s">
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122" t="s">
         <v>422</v>
       </c>
-      <c r="M122" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q122" t="s">
+      <c r="N122" t="s">
+        <v>24</v>
+      </c>
+      <c r="R122" t="s">
         <v>196</v>
       </c>
-      <c r="R122" t="s">
+      <c r="S122" t="s">
         <v>355</v>
       </c>
-      <c r="S122" t="s">
-        <v>24</v>
-      </c>
       <c r="T122" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>512</v>
       </c>
       <c r="B123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="C123">
         <v>11</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>423</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>393</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="L123" t="s">
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>4</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" t="s">
         <v>425</v>
       </c>
-      <c r="M123" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q123" t="s">
+      <c r="N123" t="s">
+        <v>24</v>
+      </c>
+      <c r="R123" t="s">
         <v>196</v>
       </c>
-      <c r="R123" t="s">
+      <c r="S123" t="s">
         <v>426</v>
       </c>
-      <c r="S123" t="s">
-        <v>24</v>
-      </c>
       <c r="T123" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="124" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>512</v>
       </c>
       <c r="B124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="C124">
         <v>28</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>427</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>393</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="F124" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="L124" t="s">
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>4</v>
+      </c>
+      <c r="K124">
+        <v>2</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124" t="s">
         <v>429</v>
       </c>
-      <c r="M124" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q124" t="s">
+      <c r="N124" t="s">
         <v>24</v>
       </c>
       <c r="R124" t="s">
@@ -6021,70 +8293,114 @@
       <c r="T124" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>512</v>
       </c>
       <c r="B125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="C125">
         <v>63</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>430</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>352</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="F125" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="L125" t="s">
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>3</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" t="s">
         <v>432</v>
       </c>
-      <c r="M125" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q125" t="s">
+      <c r="N125" t="s">
+        <v>24</v>
+      </c>
+      <c r="R125" t="s">
         <v>196</v>
       </c>
-      <c r="R125" t="s">
+      <c r="S125" t="s">
         <v>433</v>
       </c>
-      <c r="S125" t="s">
-        <v>24</v>
-      </c>
       <c r="T125" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="126" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>512</v>
       </c>
       <c r="B126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="C126">
         <v>90</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>434</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>352</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="F126" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L126" t="s">
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>4</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" t="s">
         <v>436</v>
       </c>
-      <c r="M126">
-        <v>2</v>
-      </c>
-      <c r="N126" s="1" t="s">
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Q126" t="s">
-        <v>24</v>
-      </c>
       <c r="R126" t="s">
         <v>24</v>
       </c>
@@ -6094,100 +8410,166 @@
       <c r="T126" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>512</v>
       </c>
       <c r="B127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="C127">
         <v>15</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
         <v>437</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>408</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="L127" t="s">
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>3</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" t="s">
         <v>439</v>
       </c>
-      <c r="M127" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q127" t="s">
+      <c r="N127" t="s">
+        <v>24</v>
+      </c>
+      <c r="R127" t="s">
         <v>196</v>
       </c>
-      <c r="R127" t="s">
+      <c r="S127" t="s">
         <v>440</v>
       </c>
-      <c r="S127" t="s">
-        <v>24</v>
-      </c>
       <c r="T127" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U127" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>512</v>
       </c>
       <c r="B128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="C128">
         <v>48</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>441</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>352</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="L128" t="s">
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128" t="s">
         <v>443</v>
       </c>
-      <c r="M128" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q128" t="s">
+      <c r="N128" t="s">
+        <v>24</v>
+      </c>
+      <c r="R128" t="s">
         <v>196</v>
       </c>
-      <c r="R128" t="s">
+      <c r="S128" t="s">
         <v>355</v>
       </c>
-      <c r="S128" t="s">
-        <v>24</v>
-      </c>
       <c r="T128" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U128" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>512</v>
       </c>
       <c r="B129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="C129">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>444</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>344</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="F129" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="L129" t="s">
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129" t="s">
         <v>446</v>
       </c>
-      <c r="M129" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q129" t="s">
+      <c r="N129" t="s">
         <v>24</v>
       </c>
       <c r="R129" t="s">
@@ -6199,30 +8581,52 @@
       <c r="T129" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>512</v>
       </c>
       <c r="B130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="C130">
         <v>69</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>447</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>393</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="F130" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="L130" t="s">
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>7</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" t="s">
         <v>449</v>
       </c>
-      <c r="M130" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q130" t="s">
+      <c r="N130" t="s">
         <v>24</v>
       </c>
       <c r="R130" t="s">
@@ -6234,100 +8638,166 @@
       <c r="T130" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U130" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>512</v>
       </c>
       <c r="B131">
+        <f t="shared" ref="B131:B151" si="2">ROW()-1</f>
+        <v>130</v>
+      </c>
+      <c r="C131">
         <v>52</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
         <v>441</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>352</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="F131" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="L131" t="s">
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131" t="s">
         <v>451</v>
       </c>
-      <c r="M131" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q131" t="s">
+      <c r="N131" t="s">
+        <v>24</v>
+      </c>
+      <c r="R131" t="s">
         <v>196</v>
       </c>
-      <c r="R131" t="s">
+      <c r="S131" t="s">
         <v>355</v>
       </c>
-      <c r="S131" t="s">
-        <v>24</v>
-      </c>
       <c r="T131" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>512</v>
       </c>
       <c r="B132">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+      <c r="C132">
         <v>42</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>452</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>352</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="L132" t="s">
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>2</v>
+      </c>
+      <c r="K132">
+        <v>4</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="s">
         <v>454</v>
       </c>
-      <c r="M132" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q132" t="s">
+      <c r="N132" t="s">
+        <v>24</v>
+      </c>
+      <c r="R132" t="s">
         <v>196</v>
       </c>
-      <c r="R132" t="s">
+      <c r="S132" t="s">
         <v>355</v>
       </c>
-      <c r="S132" t="s">
-        <v>24</v>
-      </c>
       <c r="T132" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>512</v>
       </c>
       <c r="B133">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+      <c r="C133">
         <v>112</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>455</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>352</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="L133" t="s">
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>2</v>
+      </c>
+      <c r="K133">
+        <v>3</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="s">
         <v>457</v>
       </c>
-      <c r="M133" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q133" t="s">
+      <c r="N133" t="s">
         <v>24</v>
       </c>
       <c r="R133" t="s">
@@ -6339,35 +8809,57 @@
       <c r="T133" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>512</v>
       </c>
       <c r="B134">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="C134">
         <v>51</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>458</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
         <v>393</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="L134" t="s">
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>3</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134" t="s">
         <v>460</v>
       </c>
-      <c r="M134">
-        <v>2</v>
-      </c>
-      <c r="N134" s="1" t="s">
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="Q134" t="s">
-        <v>24</v>
-      </c>
       <c r="R134" t="s">
         <v>24</v>
       </c>
@@ -6377,65 +8869,109 @@
       <c r="T134" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U134" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>512</v>
       </c>
       <c r="B135">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="C135">
         <v>61</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>461</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>352</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="L135" t="s">
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="s">
         <v>463</v>
       </c>
-      <c r="M135" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q135" t="s">
+      <c r="N135" t="s">
+        <v>24</v>
+      </c>
+      <c r="R135" t="s">
         <v>196</v>
       </c>
-      <c r="R135" t="s">
+      <c r="S135" t="s">
         <v>355</v>
       </c>
-      <c r="S135" t="s">
-        <v>24</v>
-      </c>
       <c r="T135" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>512</v>
       </c>
       <c r="B136">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="C136">
         <v>14</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>464</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>348</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="L136" t="s">
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>4</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="s">
         <v>466</v>
       </c>
-      <c r="M136" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q136" t="s">
+      <c r="N136" t="s">
         <v>24</v>
       </c>
       <c r="R136" t="s">
@@ -6447,65 +8983,109 @@
       <c r="T136" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>512</v>
       </c>
       <c r="B137">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+      <c r="C137">
         <v>10</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>467</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>352</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="F137" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="L137" t="s">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="s">
         <v>469</v>
       </c>
-      <c r="M137" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q137" t="s">
+      <c r="N137" t="s">
         <v>24</v>
       </c>
       <c r="R137" t="s">
         <v>24</v>
       </c>
       <c r="S137" t="s">
+        <v>24</v>
+      </c>
+      <c r="T137" t="s">
         <v>386</v>
       </c>
-      <c r="T137" t="s">
+      <c r="U137" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>512</v>
       </c>
       <c r="B138">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+      <c r="C138">
         <v>106</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>470</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>352</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="L138" t="s">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="s">
         <v>472</v>
       </c>
-      <c r="M138" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q138" t="s">
+      <c r="N138" t="s">
         <v>24</v>
       </c>
       <c r="R138" t="s">
@@ -6517,65 +9097,109 @@
       <c r="T138" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U138" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>512</v>
       </c>
       <c r="B139">
-        <v>2</v>
-      </c>
-      <c r="C139" t="s">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+      <c r="C139">
+        <v>2</v>
+      </c>
+      <c r="D139" t="s">
         <v>473</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>408</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="L139" t="s">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="s">
         <v>475</v>
       </c>
-      <c r="M139" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q139" t="s">
+      <c r="N139" t="s">
+        <v>24</v>
+      </c>
+      <c r="R139" t="s">
         <v>196</v>
       </c>
-      <c r="R139" t="s">
+      <c r="S139" t="s">
         <v>476</v>
       </c>
-      <c r="S139" t="s">
-        <v>24</v>
-      </c>
       <c r="T139" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U139" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>512</v>
       </c>
       <c r="B140">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+      <c r="C140">
         <v>31</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>444</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>357</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="L140" t="s">
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>4</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" t="s">
         <v>478</v>
       </c>
-      <c r="M140" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q140" t="s">
+      <c r="N140" t="s">
         <v>24</v>
       </c>
       <c r="R140" t="s">
@@ -6587,30 +9211,52 @@
       <c r="T140" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>512</v>
       </c>
       <c r="B141">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="C141">
         <v>45</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
         <v>458</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>357</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="L141" t="s">
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141" t="s">
         <v>480</v>
       </c>
-      <c r="M141" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q141" t="s">
+      <c r="N141" t="s">
         <v>24</v>
       </c>
       <c r="R141" t="s">
@@ -6622,35 +9268,57 @@
       <c r="T141" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>512</v>
       </c>
       <c r="B142">
-        <v>24</v>
-      </c>
-      <c r="C142" t="s">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+      <c r="C142">
+        <v>24</v>
+      </c>
+      <c r="D142" t="s">
         <v>481</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>362</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="L142" t="s">
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142" t="s">
         <v>483</v>
       </c>
-      <c r="M142">
+      <c r="N142">
         <v>9</v>
       </c>
-      <c r="N142" s="1" t="s">
+      <c r="O142" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="Q142" t="s">
-        <v>24</v>
-      </c>
       <c r="R142" t="s">
         <v>24</v>
       </c>
@@ -6660,30 +9328,52 @@
       <c r="T142" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="143" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>512</v>
       </c>
       <c r="B143">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="C143">
         <v>40</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
         <v>485</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>357</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="L143" t="s">
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>3</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143" t="s">
         <v>487</v>
       </c>
-      <c r="M143" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q143" t="s">
+      <c r="N143" t="s">
         <v>24</v>
       </c>
       <c r="R143" t="s">
@@ -6695,30 +9385,52 @@
       <c r="T143" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="144" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>512</v>
       </c>
       <c r="B144">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="C144">
         <v>12</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>488</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>408</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L144" t="s">
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>2</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144" t="s">
         <v>490</v>
       </c>
-      <c r="M144" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q144" t="s">
+      <c r="N144" t="s">
         <v>24</v>
       </c>
       <c r="R144" t="s">
@@ -6730,35 +9442,57 @@
       <c r="T144" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>512</v>
       </c>
       <c r="B145">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="C145">
         <v>30</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
         <v>382</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>362</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="L145" t="s">
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>2</v>
+      </c>
+      <c r="K145">
+        <v>2</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145" t="s">
         <v>492</v>
       </c>
-      <c r="M145">
+      <c r="N145">
         <v>10</v>
       </c>
-      <c r="N145" s="1" t="s">
+      <c r="O145" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="Q145" t="s">
-        <v>24</v>
-      </c>
       <c r="R145" t="s">
         <v>24</v>
       </c>
@@ -6768,65 +9502,109 @@
       <c r="T145" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U145" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>512</v>
       </c>
       <c r="B146">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="C146">
         <v>47</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>494</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>352</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="F146" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="L146" t="s">
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>4</v>
+      </c>
+      <c r="K146">
+        <v>3</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146" t="s">
         <v>496</v>
       </c>
-      <c r="M146" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q146" t="s">
+      <c r="N146" t="s">
+        <v>24</v>
+      </c>
+      <c r="R146" t="s">
         <v>196</v>
       </c>
-      <c r="R146" t="s">
+      <c r="S146" t="s">
         <v>355</v>
       </c>
-      <c r="S146" t="s">
-        <v>24</v>
-      </c>
       <c r="T146" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U146" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>512</v>
       </c>
       <c r="B147">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+      <c r="C147">
         <v>118</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>392</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>352</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="L147" t="s">
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>3</v>
+      </c>
+      <c r="K147">
+        <v>3</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147" t="s">
         <v>498</v>
       </c>
-      <c r="M147" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q147" t="s">
+      <c r="N147" t="s">
         <v>24</v>
       </c>
       <c r="R147" t="s">
@@ -6838,30 +9616,52 @@
       <c r="T147" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U147" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>512</v>
       </c>
       <c r="B148">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="C148">
         <v>115</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>499</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
         <v>352</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="L148" t="s">
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>2</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148" t="s">
         <v>501</v>
       </c>
-      <c r="M148" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q148" t="s">
+      <c r="N148" t="s">
         <v>24</v>
       </c>
       <c r="R148" t="s">
@@ -6873,30 +9673,52 @@
       <c r="T148" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U148" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>512</v>
       </c>
       <c r="B149">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+      <c r="C149">
         <v>85</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>502</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>352</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="F149" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="L149" t="s">
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149" t="s">
         <v>504</v>
       </c>
-      <c r="M149" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q149" t="s">
+      <c r="N149" t="s">
         <v>24</v>
       </c>
       <c r="R149" t="s">
@@ -6908,30 +9730,52 @@
       <c r="T149" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>512</v>
       </c>
       <c r="B150">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+      <c r="C150">
         <v>61</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>505</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>393</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="F150" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="L150" t="s">
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>2</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150" t="s">
         <v>507</v>
       </c>
-      <c r="M150" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q150" t="s">
+      <c r="N150" t="s">
         <v>24</v>
       </c>
       <c r="R150" t="s">
@@ -6943,35 +9787,57 @@
       <c r="T150" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>512</v>
       </c>
       <c r="B151">
-        <v>24</v>
-      </c>
-      <c r="C151" t="s">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="C151">
+        <v>24</v>
+      </c>
+      <c r="D151" t="s">
         <v>508</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>408</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="F151" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="L151" t="s">
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151" t="s">
         <v>510</v>
       </c>
-      <c r="M151">
-        <v>1</v>
-      </c>
-      <c r="N151" s="1" t="s">
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="Q151" t="s">
-        <v>24</v>
-      </c>
       <c r="R151" t="s">
         <v>24</v>
       </c>
@@ -6979,6 +9845,9 @@
         <v>24</v>
       </c>
       <c r="T151" t="s">
+        <v>24</v>
+      </c>
+      <c r="U151" t="s">
         <v>24</v>
       </c>
     </row>

--- a/data/comments/comments_relij_coded.xlsx
+++ b/data/comments/comments_relij_coded.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joellattmann/Documents/GitHub/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793C21FE-89DD-E043-A760-6E0995B75112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E460FE-8C3B-F746-BADB-974E9823FF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1080" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
   </bookViews>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60">
         <v>2</v>
@@ -5114,7 +5114,7 @@
         <v>3</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="s">
         <v>232</v>
@@ -5156,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>1</v>
@@ -5369,7 +5369,7 @@
         <v>2</v>
       </c>
       <c r="L70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="s">
         <v>250</v>
@@ -5468,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72">
         <v>2</v>
@@ -5519,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73">
         <v>2</v>
@@ -5564,13 +5564,13 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74">
         <v>3</v>
@@ -5783,7 +5783,7 @@
         <v>2</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="s">
         <v>273</v>
@@ -5885,10 +5885,10 @@
         <v>2</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="s">
         <v>279</v>
@@ -5936,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93">
         <v>2</v>
@@ -6749,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>3</v>
       </c>
       <c r="K98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6905,13 +6905,13 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100">
         <v>2</v>
       </c>
       <c r="K100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7286,7 +7286,7 @@
         <v>366</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -7298,7 +7298,7 @@
         <v>4</v>
       </c>
       <c r="K107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K114">
         <v>1</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="H120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -8210,16 +8210,16 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123">
         <v>2</v>
       </c>
       <c r="K123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" t="s">
         <v>425</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127">
         <v>3</v>
@@ -8501,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128">
         <v>1</v>
@@ -8897,13 +8897,13 @@
         <v>0</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135">
         <v>1</v>
       </c>
       <c r="J135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135">
         <v>2</v>
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -9473,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145">
         <v>2</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L148">
         <v>0</v>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -9767,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="K150">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -9824,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L151">
         <v>0</v>

--- a/data/comments/comments_relij_coded.xlsx
+++ b/data/comments/comments_relij_coded.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joellattmann/Documents/GitHub/like_dislike/data/comments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuginkha/Documents/Mediapsychology/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E460FE-8C3B-F746-BADB-974E9823FF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815351D2-42B8-5248-AD78-D1EBCE2D36CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="1080" windowWidth="28240" windowHeight="17240" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15000" windowHeight="18980" xr2:uid="{C9AD2365-A4B4-C54D-88D5-467A9B3C82F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1678,7 +1678,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1698,7 +1698,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L148">
         <v>0</v>
@@ -9767,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="K150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L150">
         <v>0</v>
